--- a/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR MAGNETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR MAGNETO.xlsx
@@ -95,7 +95,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -362,7 +362,9 @@
       <c r="C2" s="4">
         <v>4.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -396,7 +398,9 @@
       <c r="C3" s="4">
         <v>10.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>12.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
